--- a/resources/templates/standard/J4100-01.xlsx
+++ b/resources/templates/standard/J4100-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="31">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>도면 관리 대장</t>
   </si>
@@ -739,13 +742,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -779,7 +784,7 @@
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
@@ -834,7 +839,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM2" s="5"/>
       <c r="AN2" s="5"/>
@@ -889,7 +894,7 @@
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM3" s="7"/>
       <c r="AN3" s="7"/>
@@ -907,11 +912,11 @@
     </row>
     <row r="4" ht="14.1" customHeight="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -924,13 +929,13 @@
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
       <c r="N4" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O4" s="11"/>
       <c r="P4" s="11"/>
       <c r="Q4" s="11"/>
       <c r="R4" s="12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S4" s="12"/>
       <c r="T4" s="12"/>
@@ -938,7 +943,7 @@
       <c r="V4" s="12"/>
       <c r="W4" s="12"/>
       <c r="X4" s="12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4" s="12"/>
       <c r="Z4" s="12"/>
@@ -947,7 +952,7 @@
       <c r="AC4" s="12"/>
       <c r="AD4" s="12"/>
       <c r="AE4" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF4" s="12"/>
       <c r="AG4" s="12"/>
@@ -956,7 +961,7 @@
       <c r="AJ4" s="12"/>
       <c r="AK4" s="12"/>
       <c r="AL4" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM4" s="12"/>
       <c r="AN4" s="12"/>
@@ -965,7 +970,7 @@
       <c r="AQ4" s="12"/>
       <c r="AR4" s="12"/>
       <c r="AS4" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT4" s="12"/>
       <c r="AU4" s="12"/>
@@ -978,7 +983,7 @@
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
@@ -991,13 +996,13 @@
       <c r="L5" s="15"/>
       <c r="M5" s="15"/>
       <c r="N5" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O5" s="16"/>
       <c r="P5" s="16"/>
       <c r="Q5" s="16"/>
       <c r="R5" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S5" s="17"/>
       <c r="T5" s="17"/>
@@ -1052,7 +1057,7 @@
       <c r="P6" s="16"/>
       <c r="Q6" s="16"/>
       <c r="R6" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S6" s="19"/>
       <c r="T6" s="19"/>
@@ -1092,7 +1097,7 @@
       <c r="A7" s="13"/>
       <c r="B7" s="13"/>
       <c r="C7" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
@@ -1109,7 +1114,7 @@
       <c r="P7" s="16"/>
       <c r="Q7" s="16"/>
       <c r="R7" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S7" s="19"/>
       <c r="T7" s="19"/>
@@ -1164,7 +1169,7 @@
       <c r="P8" s="16"/>
       <c r="Q8" s="16"/>
       <c r="R8" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S8" s="19"/>
       <c r="T8" s="19"/>
@@ -1204,7 +1209,7 @@
       <c r="A9" s="13"/>
       <c r="B9" s="13"/>
       <c r="C9" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="21"/>
@@ -1221,7 +1226,7 @@
       <c r="P9" s="16"/>
       <c r="Q9" s="16"/>
       <c r="R9" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S9" s="19"/>
       <c r="T9" s="19"/>
@@ -1276,7 +1281,7 @@
       <c r="P10" s="16"/>
       <c r="Q10" s="16"/>
       <c r="R10" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S10" s="23"/>
       <c r="T10" s="23"/>
@@ -1316,7 +1321,7 @@
       <c r="A11" s="13"/>
       <c r="B11" s="13"/>
       <c r="C11" s="21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="21"/>
       <c r="E11" s="21"/>
@@ -1333,7 +1338,7 @@
       <c r="P11" s="16"/>
       <c r="Q11" s="16"/>
       <c r="R11" s="24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S11" s="24"/>
       <c r="T11" s="24"/>
@@ -1341,7 +1346,7 @@
       <c r="V11" s="24"/>
       <c r="W11" s="24"/>
       <c r="X11" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y11" s="25"/>
       <c r="Z11" s="25"/>
@@ -1350,7 +1355,7 @@
       <c r="AC11" s="25"/>
       <c r="AD11" s="25"/>
       <c r="AE11" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF11" s="25"/>
       <c r="AG11" s="25"/>
@@ -1359,7 +1364,7 @@
       <c r="AJ11" s="25"/>
       <c r="AK11" s="25"/>
       <c r="AL11" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM11" s="25"/>
       <c r="AN11" s="25"/>
@@ -1368,7 +1373,7 @@
       <c r="AQ11" s="25"/>
       <c r="AR11" s="25"/>
       <c r="AS11" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT11" s="25"/>
       <c r="AU11" s="25"/>
@@ -1396,7 +1401,7 @@
       <c r="P12" s="16"/>
       <c r="Q12" s="16"/>
       <c r="R12" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S12" s="26"/>
       <c r="T12" s="26"/>
@@ -1404,7 +1409,7 @@
       <c r="V12" s="26"/>
       <c r="W12" s="26"/>
       <c r="X12" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y12" s="27"/>
       <c r="Z12" s="27"/>
@@ -1413,7 +1418,7 @@
       <c r="AC12" s="27"/>
       <c r="AD12" s="27"/>
       <c r="AE12" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF12" s="27"/>
       <c r="AG12" s="27"/>
@@ -1422,7 +1427,7 @@
       <c r="AJ12" s="27"/>
       <c r="AK12" s="27"/>
       <c r="AL12" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM12" s="27"/>
       <c r="AN12" s="27"/>
@@ -1431,7 +1436,7 @@
       <c r="AQ12" s="27"/>
       <c r="AR12" s="27"/>
       <c r="AS12" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT12" s="27"/>
       <c r="AU12" s="27"/>
@@ -1444,7 +1449,7 @@
       <c r="A13" s="13"/>
       <c r="B13" s="13"/>
       <c r="C13" s="28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" s="28"/>
       <c r="E13" s="28"/>
@@ -1461,7 +1466,7 @@
       <c r="P13" s="16"/>
       <c r="Q13" s="16"/>
       <c r="R13" s="23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S13" s="23"/>
       <c r="T13" s="23"/>
@@ -1516,7 +1521,7 @@
       <c r="P14" s="16"/>
       <c r="Q14" s="16"/>
       <c r="R14" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S14" s="30"/>
       <c r="T14" s="30"/>
@@ -1556,7 +1561,7 @@
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14"/>
@@ -1569,13 +1574,13 @@
       <c r="L15" s="15"/>
       <c r="M15" s="15"/>
       <c r="N15" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O15" s="16"/>
       <c r="P15" s="16"/>
       <c r="Q15" s="16"/>
       <c r="R15" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S15" s="17"/>
       <c r="T15" s="17"/>
@@ -1630,7 +1635,7 @@
       <c r="P16" s="16"/>
       <c r="Q16" s="16"/>
       <c r="R16" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S16" s="19"/>
       <c r="T16" s="19"/>
@@ -1670,7 +1675,7 @@
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" s="21"/>
       <c r="E17" s="21"/>
@@ -1687,7 +1692,7 @@
       <c r="P17" s="16"/>
       <c r="Q17" s="16"/>
       <c r="R17" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S17" s="19"/>
       <c r="T17" s="19"/>
@@ -1742,7 +1747,7 @@
       <c r="P18" s="16"/>
       <c r="Q18" s="16"/>
       <c r="R18" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S18" s="19"/>
       <c r="T18" s="19"/>
@@ -1782,7 +1787,7 @@
       <c r="A19" s="13"/>
       <c r="B19" s="13"/>
       <c r="C19" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="21"/>
       <c r="E19" s="21"/>
@@ -1799,7 +1804,7 @@
       <c r="P19" s="16"/>
       <c r="Q19" s="16"/>
       <c r="R19" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S19" s="19"/>
       <c r="T19" s="19"/>
@@ -1854,7 +1859,7 @@
       <c r="P20" s="16"/>
       <c r="Q20" s="16"/>
       <c r="R20" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S20" s="23"/>
       <c r="T20" s="23"/>
@@ -1894,7 +1899,7 @@
       <c r="A21" s="13"/>
       <c r="B21" s="13"/>
       <c r="C21" s="21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="21"/>
       <c r="E21" s="21"/>
@@ -1911,7 +1916,7 @@
       <c r="P21" s="16"/>
       <c r="Q21" s="16"/>
       <c r="R21" s="24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S21" s="24"/>
       <c r="T21" s="24"/>
@@ -1919,7 +1924,7 @@
       <c r="V21" s="24"/>
       <c r="W21" s="24"/>
       <c r="X21" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y21" s="25"/>
       <c r="Z21" s="25"/>
@@ -1928,7 +1933,7 @@
       <c r="AC21" s="25"/>
       <c r="AD21" s="25"/>
       <c r="AE21" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF21" s="25"/>
       <c r="AG21" s="25"/>
@@ -1937,7 +1942,7 @@
       <c r="AJ21" s="25"/>
       <c r="AK21" s="25"/>
       <c r="AL21" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM21" s="25"/>
       <c r="AN21" s="25"/>
@@ -1946,7 +1951,7 @@
       <c r="AQ21" s="25"/>
       <c r="AR21" s="25"/>
       <c r="AS21" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT21" s="25"/>
       <c r="AU21" s="25"/>
@@ -1974,7 +1979,7 @@
       <c r="P22" s="16"/>
       <c r="Q22" s="16"/>
       <c r="R22" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S22" s="26"/>
       <c r="T22" s="26"/>
@@ -1982,7 +1987,7 @@
       <c r="V22" s="26"/>
       <c r="W22" s="26"/>
       <c r="X22" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y22" s="27"/>
       <c r="Z22" s="27"/>
@@ -1991,7 +1996,7 @@
       <c r="AC22" s="27"/>
       <c r="AD22" s="27"/>
       <c r="AE22" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF22" s="27"/>
       <c r="AG22" s="27"/>
@@ -2000,7 +2005,7 @@
       <c r="AJ22" s="27"/>
       <c r="AK22" s="27"/>
       <c r="AL22" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM22" s="27"/>
       <c r="AN22" s="27"/>
@@ -2009,7 +2014,7 @@
       <c r="AQ22" s="27"/>
       <c r="AR22" s="27"/>
       <c r="AS22" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT22" s="27"/>
       <c r="AU22" s="27"/>
@@ -2022,7 +2027,7 @@
       <c r="A23" s="13"/>
       <c r="B23" s="13"/>
       <c r="C23" s="28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23" s="28"/>
       <c r="E23" s="28"/>
@@ -2039,7 +2044,7 @@
       <c r="P23" s="16"/>
       <c r="Q23" s="16"/>
       <c r="R23" s="23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S23" s="23"/>
       <c r="T23" s="23"/>
@@ -2094,7 +2099,7 @@
       <c r="P24" s="16"/>
       <c r="Q24" s="16"/>
       <c r="R24" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S24" s="30"/>
       <c r="T24" s="30"/>
@@ -2134,7 +2139,7 @@
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
@@ -2147,13 +2152,13 @@
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O25" s="16"/>
       <c r="P25" s="16"/>
       <c r="Q25" s="16"/>
       <c r="R25" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S25" s="17"/>
       <c r="T25" s="17"/>
@@ -2208,7 +2213,7 @@
       <c r="P26" s="16"/>
       <c r="Q26" s="16"/>
       <c r="R26" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S26" s="19"/>
       <c r="T26" s="19"/>
@@ -2248,7 +2253,7 @@
       <c r="A27" s="13"/>
       <c r="B27" s="13"/>
       <c r="C27" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" s="21"/>
       <c r="E27" s="21"/>
@@ -2265,7 +2270,7 @@
       <c r="P27" s="16"/>
       <c r="Q27" s="16"/>
       <c r="R27" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S27" s="19"/>
       <c r="T27" s="19"/>
@@ -2320,7 +2325,7 @@
       <c r="P28" s="16"/>
       <c r="Q28" s="16"/>
       <c r="R28" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S28" s="19"/>
       <c r="T28" s="19"/>
@@ -2360,7 +2365,7 @@
       <c r="A29" s="13"/>
       <c r="B29" s="13"/>
       <c r="C29" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D29" s="21"/>
       <c r="E29" s="21"/>
@@ -2377,7 +2382,7 @@
       <c r="P29" s="16"/>
       <c r="Q29" s="16"/>
       <c r="R29" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S29" s="19"/>
       <c r="T29" s="19"/>
@@ -2432,7 +2437,7 @@
       <c r="P30" s="16"/>
       <c r="Q30" s="16"/>
       <c r="R30" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S30" s="23"/>
       <c r="T30" s="23"/>
@@ -2472,7 +2477,7 @@
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D31" s="21"/>
       <c r="E31" s="21"/>
@@ -2489,7 +2494,7 @@
       <c r="P31" s="16"/>
       <c r="Q31" s="16"/>
       <c r="R31" s="24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S31" s="24"/>
       <c r="T31" s="24"/>
@@ -2497,7 +2502,7 @@
       <c r="V31" s="24"/>
       <c r="W31" s="24"/>
       <c r="X31" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y31" s="25"/>
       <c r="Z31" s="25"/>
@@ -2506,7 +2511,7 @@
       <c r="AC31" s="25"/>
       <c r="AD31" s="25"/>
       <c r="AE31" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF31" s="25"/>
       <c r="AG31" s="25"/>
@@ -2515,7 +2520,7 @@
       <c r="AJ31" s="25"/>
       <c r="AK31" s="25"/>
       <c r="AL31" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM31" s="25"/>
       <c r="AN31" s="25"/>
@@ -2524,7 +2529,7 @@
       <c r="AQ31" s="25"/>
       <c r="AR31" s="25"/>
       <c r="AS31" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT31" s="25"/>
       <c r="AU31" s="25"/>
@@ -2552,7 +2557,7 @@
       <c r="P32" s="16"/>
       <c r="Q32" s="16"/>
       <c r="R32" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S32" s="26"/>
       <c r="T32" s="26"/>
@@ -2560,7 +2565,7 @@
       <c r="V32" s="26"/>
       <c r="W32" s="26"/>
       <c r="X32" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y32" s="27"/>
       <c r="Z32" s="27"/>
@@ -2569,7 +2574,7 @@
       <c r="AC32" s="27"/>
       <c r="AD32" s="27"/>
       <c r="AE32" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF32" s="27"/>
       <c r="AG32" s="27"/>
@@ -2578,7 +2583,7 @@
       <c r="AJ32" s="27"/>
       <c r="AK32" s="27"/>
       <c r="AL32" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM32" s="27"/>
       <c r="AN32" s="27"/>
@@ -2587,7 +2592,7 @@
       <c r="AQ32" s="27"/>
       <c r="AR32" s="27"/>
       <c r="AS32" s="27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT32" s="27"/>
       <c r="AU32" s="27"/>
@@ -2600,7 +2605,7 @@
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
@@ -2617,7 +2622,7 @@
       <c r="P33" s="16"/>
       <c r="Q33" s="16"/>
       <c r="R33" s="23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S33" s="23"/>
       <c r="T33" s="23"/>
@@ -2672,7 +2677,7 @@
       <c r="P34" s="16"/>
       <c r="Q34" s="16"/>
       <c r="R34" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="S34" s="32"/>
       <c r="T34" s="32"/>
